--- a/artfynd/A 41563-2024 artfynd.xlsx
+++ b/artfynd/A 41563-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120406569</v>
+        <v>120406580</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>417283</v>
+        <v>417473</v>
       </c>
       <c r="R2" t="n">
-        <v>7017870</v>
+        <v>7018595</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -785,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120406570</v>
+        <v>120406578</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>417198</v>
+        <v>417494</v>
       </c>
       <c r="R3" t="n">
-        <v>7018000</v>
+        <v>7018608</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -895,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120406579</v>
+        <v>120406575</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>417339</v>
+        <v>417209</v>
       </c>
       <c r="R4" t="n">
-        <v>7018564</v>
+        <v>7018189</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -997,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120406577</v>
+        <v>120406570</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,34 +997,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>417480</v>
+        <v>417198</v>
       </c>
       <c r="R5" t="n">
-        <v>7018592</v>
+        <v>7018000</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120406580</v>
+        <v>120406576</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417473</v>
+        <v>417368</v>
       </c>
       <c r="R6" t="n">
-        <v>7018595</v>
+        <v>7018576</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1201,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120406576</v>
+        <v>120406569</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,34 +1209,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417368</v>
+        <v>417283</v>
       </c>
       <c r="R7" t="n">
-        <v>7018576</v>
+        <v>7017870</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1303,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120406575</v>
+        <v>120406579</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,21 +1319,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>417209</v>
+        <v>417339</v>
       </c>
       <c r="R8" t="n">
-        <v>7018189</v>
+        <v>7018564</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1405,7 +1405,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120406578</v>
+        <v>120406577</v>
       </c>
       <c r="B9" t="n">
         <v>90598</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>417494</v>
+        <v>417480</v>
       </c>
       <c r="R9" t="n">
-        <v>7018608</v>
+        <v>7018592</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>

--- a/artfynd/A 41563-2024 artfynd.xlsx
+++ b/artfynd/A 41563-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120406578</v>
+        <v>120406575</v>
       </c>
       <c r="B3" t="n">
         <v>90598</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>417494</v>
+        <v>417209</v>
       </c>
       <c r="R3" t="n">
-        <v>7018608</v>
+        <v>7018189</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120406575</v>
+        <v>120406576</v>
       </c>
       <c r="B4" t="n">
         <v>90598</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>417209</v>
+        <v>417368</v>
       </c>
       <c r="R4" t="n">
-        <v>7018189</v>
+        <v>7018576</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120406570</v>
+        <v>120406579</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>417198</v>
+        <v>417339</v>
       </c>
       <c r="R5" t="n">
-        <v>7018000</v>
+        <v>7018564</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120406576</v>
+        <v>120406577</v>
       </c>
       <c r="B6" t="n">
         <v>90598</v>
@@ -1131,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417368</v>
+        <v>417480</v>
       </c>
       <c r="R6" t="n">
-        <v>7018576</v>
+        <v>7018592</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1193,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120406569</v>
+        <v>120406578</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,42 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417283</v>
+        <v>417494</v>
       </c>
       <c r="R7" t="n">
-        <v>7017870</v>
+        <v>7018608</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1303,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120406579</v>
+        <v>120406570</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,34 +1303,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>417339</v>
+        <v>417198</v>
       </c>
       <c r="R8" t="n">
-        <v>7018564</v>
+        <v>7018000</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1405,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120406577</v>
+        <v>120406569</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>417480</v>
+        <v>417283</v>
       </c>
       <c r="R9" t="n">
-        <v>7018592</v>
+        <v>7017870</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>

--- a/artfynd/A 41563-2024 artfynd.xlsx
+++ b/artfynd/A 41563-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120406575</v>
+        <v>120406578</v>
       </c>
       <c r="B3" t="n">
         <v>90598</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>417209</v>
+        <v>417494</v>
       </c>
       <c r="R3" t="n">
-        <v>7018189</v>
+        <v>7018608</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120406576</v>
+        <v>120406575</v>
       </c>
       <c r="B4" t="n">
         <v>90598</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>417368</v>
+        <v>417209</v>
       </c>
       <c r="R4" t="n">
-        <v>7018576</v>
+        <v>7018189</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120406579</v>
+        <v>120406577</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>417339</v>
+        <v>417480</v>
       </c>
       <c r="R5" t="n">
-        <v>7018564</v>
+        <v>7018592</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120406577</v>
+        <v>120406576</v>
       </c>
       <c r="B6" t="n">
         <v>90598</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417480</v>
+        <v>417368</v>
       </c>
       <c r="R6" t="n">
-        <v>7018592</v>
+        <v>7018576</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120406578</v>
+        <v>120406569</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417494</v>
+        <v>417283</v>
       </c>
       <c r="R7" t="n">
-        <v>7018608</v>
+        <v>7017870</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1397,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120406569</v>
+        <v>120406579</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,42 +1421,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>417283</v>
+        <v>417339</v>
       </c>
       <c r="R9" t="n">
-        <v>7017870</v>
+        <v>7018564</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>

--- a/artfynd/A 41563-2024 artfynd.xlsx
+++ b/artfynd/A 41563-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120406576</v>
+        <v>120406569</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417368</v>
+        <v>417283</v>
       </c>
       <c r="R6" t="n">
-        <v>7018576</v>
+        <v>7017870</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120406569</v>
+        <v>120406576</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,42 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417283</v>
+        <v>417368</v>
       </c>
       <c r="R7" t="n">
-        <v>7017870</v>
+        <v>7018576</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>

--- a/artfynd/A 41563-2024 artfynd.xlsx
+++ b/artfynd/A 41563-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120406580</v>
+        <v>120406578</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>417473</v>
+        <v>417494</v>
       </c>
       <c r="R2" t="n">
-        <v>7018595</v>
+        <v>7018608</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120406578</v>
+        <v>120406570</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>417494</v>
+        <v>417198</v>
       </c>
       <c r="R3" t="n">
-        <v>7018608</v>
+        <v>7018000</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120406575</v>
+        <v>120406576</v>
       </c>
       <c r="B4" t="n">
         <v>90598</v>
@@ -919,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>417209</v>
+        <v>417368</v>
       </c>
       <c r="R4" t="n">
-        <v>7018189</v>
+        <v>7018576</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1083,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120406569</v>
+        <v>120406579</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,42 +1107,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417283</v>
+        <v>417339</v>
       </c>
       <c r="R6" t="n">
-        <v>7017870</v>
+        <v>7018564</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120406576</v>
+        <v>120406580</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417368</v>
+        <v>417473</v>
       </c>
       <c r="R7" t="n">
-        <v>7018576</v>
+        <v>7018595</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120406570</v>
+        <v>120406575</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,42 +1311,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>417198</v>
+        <v>417209</v>
       </c>
       <c r="R8" t="n">
-        <v>7018000</v>
+        <v>7018189</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1405,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120406579</v>
+        <v>120406569</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>417339</v>
+        <v>417283</v>
       </c>
       <c r="R9" t="n">
-        <v>7018564</v>
+        <v>7017870</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>

--- a/artfynd/A 41563-2024 artfynd.xlsx
+++ b/artfynd/A 41563-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120406578</v>
+        <v>120406570</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>417494</v>
+        <v>417198</v>
       </c>
       <c r="R2" t="n">
-        <v>7018608</v>
+        <v>7018000</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120406570</v>
+        <v>120406578</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>417198</v>
+        <v>417494</v>
       </c>
       <c r="R3" t="n">
-        <v>7018000</v>
+        <v>7018608</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120406576</v>
+        <v>120406577</v>
       </c>
       <c r="B4" t="n">
         <v>90598</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>417368</v>
+        <v>417480</v>
       </c>
       <c r="R4" t="n">
-        <v>7018576</v>
+        <v>7018592</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120406577</v>
+        <v>120406576</v>
       </c>
       <c r="B5" t="n">
         <v>90598</v>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>417480</v>
+        <v>417368</v>
       </c>
       <c r="R5" t="n">
-        <v>7018592</v>
+        <v>7018576</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120406579</v>
+        <v>120406580</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417339</v>
+        <v>417473</v>
       </c>
       <c r="R6" t="n">
-        <v>7018564</v>
+        <v>7018595</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120406580</v>
+        <v>120406569</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,34 +1209,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417473</v>
+        <v>417283</v>
       </c>
       <c r="R7" t="n">
-        <v>7018595</v>
+        <v>7017870</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1397,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120406569</v>
+        <v>120406579</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,42 +1421,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>417283</v>
+        <v>417339</v>
       </c>
       <c r="R9" t="n">
-        <v>7017870</v>
+        <v>7018564</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>

--- a/artfynd/A 41563-2024 artfynd.xlsx
+++ b/artfynd/A 41563-2024 artfynd.xlsx
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120406580</v>
+        <v>120406569</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,34 +1107,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>417473</v>
+        <v>417283</v>
       </c>
       <c r="R6" t="n">
-        <v>7018595</v>
+        <v>7017870</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1193,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120406569</v>
+        <v>120406580</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,42 +1217,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mossaflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>417283</v>
+        <v>417473</v>
       </c>
       <c r="R7" t="n">
-        <v>7017870</v>
+        <v>7018595</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
